--- a/outputs/463-17.xlsx
+++ b/outputs/463-17.xlsx
@@ -122,12 +122,16 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -326,268 +330,268 @@
   <dimension ref="A1:D46"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="13.5" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="15.18"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="6.27"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="17.54"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="15.18"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="6.27"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="17.54"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="0" t="s">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="0" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="2" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="0" t="s">
+      <c r="A2" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B2" s="0" t="n">
-        <v>5</v>
-      </c>
-      <c r="D2" s="0" t="s">
+      <c r="B2" s="1" t="n">
+        <v>5</v>
+      </c>
+      <c r="D2" s="1" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="0" t="s">
-        <v>4</v>
-      </c>
-      <c r="B3" s="0" t="n">
+      <c r="A3" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B3" s="1" t="n">
         <v>10</v>
       </c>
-      <c r="D3" s="0" t="s">
+      <c r="D3" s="1" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="0" t="s">
-        <v>5</v>
-      </c>
-      <c r="B4" s="0" t="n">
-        <v>5</v>
-      </c>
-      <c r="D4" s="0" t="s">
+      <c r="A4" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B4" s="1" t="n">
+        <v>5</v>
+      </c>
+      <c r="D4" s="1" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="0" t="s">
-        <v>6</v>
-      </c>
-      <c r="B5" s="0" t="n">
+      <c r="A5" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B5" s="1" t="n">
         <v>25</v>
       </c>
-      <c r="D5" s="0" t="s">
+      <c r="D5" s="1" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D6" s="0" t="s">
+      <c r="D6" s="1" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D7" s="0" t="s">
+      <c r="D7" s="1" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D8" s="0" t="s">
+      <c r="D8" s="1" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D9" s="0" t="s">
+      <c r="D9" s="1" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D10" s="0" t="s">
+      <c r="D10" s="1" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D11" s="0" t="s">
+      <c r="D11" s="1" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D12" s="0" t="s">
+      <c r="D12" s="1" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D13" s="0" t="s">
+      <c r="D13" s="1" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D14" s="0" t="s">
+      <c r="D14" s="1" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D15" s="0" t="s">
+      <c r="D15" s="1" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D16" s="0" t="s">
+      <c r="D16" s="1" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D17" s="0" t="s">
+      <c r="D17" s="1" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D18" s="0" t="s">
+      <c r="D18" s="1" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D19" s="0" t="s">
+      <c r="D19" s="1" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D20" s="0" t="s">
+      <c r="D20" s="1" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D21" s="0" t="s">
+      <c r="D21" s="1" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D22" s="0" t="s">
+      <c r="D22" s="1" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D23" s="0" t="s">
+      <c r="D23" s="1" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D24" s="0" t="s">
+      <c r="D24" s="1" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D25" s="0" t="s">
+      <c r="D25" s="1" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D26" s="0" t="s">
+      <c r="D26" s="1" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D27" s="0" t="s">
+      <c r="D27" s="1" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D28" s="0" t="s">
+      <c r="D28" s="1" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D29" s="0" t="s">
+      <c r="D29" s="1" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D30" s="0" t="s">
+      <c r="D30" s="1" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D31" s="0" t="s">
+      <c r="D31" s="1" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D32" s="0" t="s">
+      <c r="D32" s="1" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D33" s="0" t="s">
+      <c r="D33" s="1" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D34" s="0" t="s">
+      <c r="D34" s="1" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D35" s="0" t="s">
+      <c r="D35" s="1" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D36" s="0" t="s">
+      <c r="D36" s="1" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D37" s="0" t="s">
+      <c r="D37" s="1" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D38" s="0" t="s">
+      <c r="D38" s="1" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D39" s="0" t="s">
+      <c r="D39" s="1" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D40" s="0" t="s">
+      <c r="D40" s="1" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D41" s="0" t="s">
+      <c r="D41" s="1" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D42" s="0" t="s">
+      <c r="D42" s="1" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D43" s="0" t="s">
+      <c r="D43" s="1" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D44" s="0" t="s">
+      <c r="D44" s="1" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D45" s="0" t="s">
+      <c r="D45" s="1" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D46" s="0" t="s">
+      <c r="D46" s="1" t="s">
         <v>6</v>
       </c>
     </row>

--- a/outputs/463-17.xlsx
+++ b/outputs/463-17.xlsx
@@ -20,15 +20,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="7">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="6">
   <si>
     <t xml:space="preserve">Company Name</t>
   </si>
   <si>
     <t xml:space="preserve">Count</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Required link this</t>
   </si>
   <si>
     <t xml:space="preserve">HP</t>
@@ -327,7 +324,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:D46"/>
+  <dimension ref="A1:D45"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="13.5" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="15.18"/>
@@ -348,46 +345,46 @@
     </row>
     <row r="2" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="1" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B2" s="1" t="n">
         <v>5</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="1" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B3" s="1" t="n">
         <v>10</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B4" s="1" t="n">
         <v>5</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B5" s="1" t="n">
         <v>25</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -397,47 +394,47 @@
     </row>
     <row r="7" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D7" s="1" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D8" s="1" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D9" s="1" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D10" s="1" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D11" s="1" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D12" s="1" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D13" s="1" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D14" s="1" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D15" s="1" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -447,22 +444,22 @@
     </row>
     <row r="17" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D17" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D18" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D19" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D20" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -472,127 +469,122 @@
     </row>
     <row r="22" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D22" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D23" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D24" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D25" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D26" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D27" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D28" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D29" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D30" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D31" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D32" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D33" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D34" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D35" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D36" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D37" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D38" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D39" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D40" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D41" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D42" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D43" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D44" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D45" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="46" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D46" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>
